--- a/astro-site/public/dl/burger-joint-checklist-templates/05-burger-restaurant-cleaning-checklist-inventory-maintenance.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/05-burger-restaurant-cleaning-checklist-inventory-maintenance.xlsx
@@ -310,11 +310,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -728,7 +728,7 @@
     <row r="6" ht="63" customHeight="1">
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>▸ The "Quarterly &amp; Annual" tab covers the maintenance you CONTRACT out and an inspector may ask to see: pest control, hood and duct cleaning (NFPA 96), extinguishers and their hydrostatic test, hood fire suppression, gas, refrigeration, used-oil pickup, waste and containers, Legionella, water, insurance, POS / sales tax and thermometer calibration.</t>
+          <t>▸ The "Quarterly &amp; Annual" tab covers the maintenance you CONTRACT out and an inspector may ask to see: pest control, hood and duct cleaning (NFPA 96), extinguishers and their hydrostatic test, hood fire suppression, gas, refrigeration, used-oil pickup, waste, containers and grease trap, Legionella, water, insurance, POS / sales tax and thermometer calibration.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="10">
         <f>IF(B8="","",IF(B8&lt;D8,"⚠️ REORDER","OK"))</f>
@@ -1142,7 +1142,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Cheddar slices</t>
+          <t>American / cheddar slices</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="14">
         <f>IF(B17="","",IF(B17&lt;D17,"⚠️ REORDER","OK"))</f>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ REORDER","OK"))</f>
@@ -1365,11 +1365,11 @@
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
         <f>IF(B26="","",IF(B26&lt;D26,"⚠️ REORDER","OK"))</f>
@@ -1386,11 +1386,11 @@
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ REORDER","OK"))</f>
@@ -1407,11 +1407,11 @@
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10">
         <f>IF(B28="","",IF(B28&lt;D28,"⚠️ REORDER","OK"))</f>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E30" s="10">
         <f>IF(B30="","",IF(B30&lt;D30,"⚠️ REORDER","OK"))</f>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="14">
         <f>IF(B31="","",IF(B31&lt;D31,"⚠️ REORDER","OK"))</f>
@@ -1720,9 +1720,9 @@
       <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>Take apart and deep-clean the flat-top griddle</t>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Deep-clean the flat-top griddle: grease trough and drawer, splash guards, front and sides (griddle brick or screen + griddle cleaner), then re-season</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
@@ -1801,7 +1801,7 @@
       <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Take down the hood filters and degrease them — the crew cleans the filters; the contractor cleans the ducts ("Quarterly &amp; Annual" tab, NFPA 96)</t>
         </is>
@@ -2145,7 +2145,7 @@
       <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Check beef dates (fresh: 3 days max, never past the supplier's date)</t>
         </is>
@@ -2172,7 +2172,7 @@
       <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Check opened cheeses: covered, opening date, not past the manufacturer's date</t>
         </is>
@@ -2199,7 +2199,7 @@
       <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Check house sauces (5 days max, kit guideline; FDA allows 7 counting prep day, 3-501.17)</t>
         </is>
@@ -2280,7 +2280,7 @@
       <c r="A11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Check no frozen product is past its shelf life (see the table at the bottom of this sheet)</t>
         </is>
@@ -2374,7 +2374,7 @@
       <c r="A15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Check fryer oil: TPM test (no federal limit; change per tester and fryer manufacturer)</t>
         </is>
@@ -2852,9 +2852,9 @@
       <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Full fryer oil change</t>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>Fryer boil-out: drain, clean with fryer cleaner and refill with fresh oil, per the manufacturer (the oil itself is changed whenever the TPM tester says, not once a month)</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -2879,7 +2879,7 @@
       <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Dish machine: filters and chemical levels (water softener salt only if you have a softener)</t>
         </is>
@@ -2906,7 +2906,7 @@
       <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Exhaust hood: check the fan motor and the filters (replace only bent or damaged ones); the contractor cleans the DUCTS (see "Quarterly &amp; Annual")</t>
         </is>
@@ -2973,7 +2973,7 @@
       <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Extinguisher: monthly visual check (gauge in the green, pin and seal intact, access clear, tag signed); the official service is by the maintainer, see "Quarterly &amp; Annual"</t>
         </is>
@@ -3250,7 +3250,7 @@
       <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Pest control by a licensed operator: service visit and signed service report on file</t>
         </is>
@@ -3273,7 +3273,7 @@
       <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Hood and duct cleaning by a certified contractor (NFPA 96): quarterly if high volume or charbroil, semiannual if moderate — the griddle and the fryers together grease up the duct fast</t>
         </is>
@@ -3296,9 +3296,9 @@
       <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="38" t="inlineStr">
-        <is>
-          <t>Annual extinguisher maintenance by a licensed fire protection company: new tag and record (OSHA 1910.157); hood fire suppression inspected every 6 months (NFPA 96)</t>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Hood fire suppression inspected every 6 months (NFPA 96) and annual extinguisher maintenance by a licensed fire protection company: new tag and record (OSHA 1910.157)</t>
         </is>
       </c>
       <c r="C8" s="29" t="n"/>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Semiannual</t>
         </is>
       </c>
       <c r="F8" s="30" t="n"/>
@@ -3319,7 +3319,7 @@
       <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Extinguisher hydrostatic test by the fire protection company: Class K (wet chemical) and CO2 units every 5 years, dry chemical as its label says (OSHA 1910.157(f); NFPA 10)</t>
         </is>
@@ -3342,7 +3342,7 @@
       <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Gas lines and appliance connections (griddle, fryers, range) checked by a licensed pro, as often as your local code requires</t>
         </is>
@@ -3365,7 +3365,7 @@
       <c r="A11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Refrigeration service by an EPA 608-certified tech: walk-in, reach-ins and the make line — coils, gaskets and refrigerant leak check</t>
         </is>
@@ -3401,9 +3401,9 @@
       <c r="A13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="38" t="inlineStr">
-        <is>
-          <t>Used fryer oil pickup by a licensed recycler: file the pickup receipts (with fryers running all day, it is one of the biggest waste streams in a burger joint)</t>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Used fryer oil: pickups by a licensed recycler as often as your volume needs; every quarter, check the receipts are on file and the outdoor container is closed and not leaking (with fryers running all day, it is one of the biggest waste streams in a burger joint)</t>
         </is>
       </c>
       <c r="C13" s="29" t="n"/>
@@ -3424,9 +3424,9 @@
       <c r="A14" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>Review the waste and recycling hauler contract and local recycling rules: takeout and delivery multiply the cardboard and packaging</t>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>Review the waste and recycling hauler contract and local recycling rules (takeout and delivery multiply the cardboard and packaging), and keep the grease trap pumping manifests, as often as your local FOG rules require</t>
         </is>
       </c>
       <c r="C14" s="29" t="n"/>
@@ -3447,7 +3447,7 @@
       <c r="A15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Legionella: if you have a cooling tower or at-risk hot water, keep a water management program as your local health code requires</t>
         </is>
@@ -3470,7 +3470,7 @@
       <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Water quality: on city water, read your utility's annual Consumer Confidence Report; on a private well or tank, test it as your health department requires; service any filter or softener per its maker</t>
         </is>
@@ -3506,7 +3506,7 @@
       <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Review insurance (general liability, property, workers' comp; liquor liability if you serve alcohol) and renewal dates</t>
         </is>
@@ -3529,7 +3529,7 @@
       <c r="A19" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>POS check: software updates, sales tax rates and settings, user permissions — plus the online ordering and delivery app integrations</t>
         </is>
@@ -3552,9 +3552,9 @@
       <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="38" t="inlineStr">
-        <is>
-          <t>Calibrate the thermometers and the griddle probe against a known standard (ice-point method, 32 °F): the core temp of ground beef depends on that probe</t>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Once a year, have the griddle thermostats and any built-in probes checked against a known standard; the probe thermometers get a daily ice-point check (32 °F) at the grill station — the core temp of ground beef depends on them</t>
         </is>
       </c>
       <c r="C20" s="29" t="n"/>
@@ -3575,7 +3575,7 @@
       <c r="A21" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Log the next service date for each contract and file the signed report</t>
         </is>
